--- a/Financial Analysis/STLA.xlsx
+++ b/Financial Analysis/STLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D7160E-05DC-4E1A-9585-7877D4E74C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973CEC1D-7C21-43B9-B167-50215D481EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{30EBCB5C-6AEB-429F-AD50-6C6253964D7E}"/>
   </bookViews>
@@ -928,14 +928,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>7.5670000000000002</v>
+        <v>9.4710000000000001</v>
       </c>
       <c r="E3" s="6">
-        <v>45868</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45925</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="6">
         <v>45960</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>21812.6342</v>
+        <v>27301.104599999999</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>31951.6342</v>
+        <v>37440.104599999999</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AF43" s="11">
         <f>Main!D3</f>
-        <v>7.5670000000000002</v>
+        <v>9.4710000000000001</v>
       </c>
     </row>
     <row r="44" spans="2:32" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AF44" s="12">
         <f>AF42/AF43-1</f>
-        <v>1.6974869917057078</v>
+        <v>1.1551984020945087</v>
       </c>
     </row>
     <row r="45" spans="2:32" x14ac:dyDescent="0.3">
@@ -5338,13 +5338,13 @@
     <row r="62" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AF62" s="15">
         <f>Main!D3</f>
-        <v>7.5670000000000002</v>
+        <v>9.4710000000000001</v>
       </c>
     </row>
     <row r="63" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AF63" s="12">
         <f>AF61/AF62-1</f>
-        <v>-0.24702314771022726</v>
+        <v>-0.39839765164431307</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/STLA.xlsx
+++ b/Financial Analysis/STLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973CEC1D-7C21-43B9-B167-50215D481EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B016E1C0-F105-46B6-9D2B-3DBAC234645A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{30EBCB5C-6AEB-429F-AD50-6C6253964D7E}"/>
   </bookViews>
@@ -935,7 +935,7 @@
       </c>
       <c r="F3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>46002</v>
       </c>
       <c r="G3" s="6">
         <v>45960</v>
